--- a/Energiehubs_Uniform_Fases_RES_REGIO.xlsx
+++ b/Energiehubs_Uniform_Fases_RES_REGIO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M365"/>
+  <dimension ref="A1:O431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,16 @@
           <t>Type Contract</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Contact email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Naam / Telefoon / Functie</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -545,6 +555,16 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>info@waterstofwijkwagenborgen.nl</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sybe bij de Leij (programmamanager Enexis); Ruud Busscher (projectleider)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,6 +616,16 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -647,6 +677,16 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -698,6 +738,16 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>info@eigenwarmtebalk.frl</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Goffe Venema (projectleider), 06-22503500; Tjeerd Osinga (bestuurslid)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -749,6 +799,16 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>info@gelderswarmtebedrijf.nl</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>GWB – Prov. Gelderland / Alliander / IEF | gelderswarmtebedrijf.nl/contact</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -800,6 +860,16 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>info@flexcitizen.nl</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>FlexCitizen – flexcitizen.nl | Sporenburg Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -851,6 +921,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Warm Lunetten Utrecht – lunetten.nl | Utrecht</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -902,6 +978,16 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>info@oogvoorwarmte.nl</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Energiecoöperatie Oog in Al / Warm Utrecht – oogvoorwarmte.nl</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -953,6 +1039,16 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,6 +1100,16 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1055,6 +1161,16 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>info@opgewekthouten.nl</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>opgewekthouten.nl | Houten, Utrecht</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1110,6 +1226,16 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>info@warmtelinq.nl</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>WarmtelinQ BV | Warmtenet Den Haag–Rotterdam corridor</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1161,6 +1287,16 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>info@hylifeinnovations.nl</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Hylife Innovations – hylifeinnovations.nl | Goeree-Overflakkee</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,6 +1348,16 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>info@hoogdalem.nl</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>hoogdalem.nl | Gorinchem, Zuid-Holland</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1263,6 +1409,16 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1314,6 +1470,16 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1365,6 +1531,16 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1416,6 +1592,16 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>info@hollandrijnland.nl</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Holland Rijnland – hollandrijnland.nl | Warmtenet</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1463,6 +1649,16 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1483,7 +1679,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burgemeester Elsenlaan, 2282 NE</t>
+          <t>Generaal Spoorlaan, 2283 GA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1510,6 +1706,16 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1557,6 +1763,16 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1604,6 +1820,16 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1651,6 +1877,16 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1698,6 +1934,16 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1745,6 +1991,16 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1792,6 +2048,16 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1839,6 +2105,16 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1886,6 +2162,16 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1933,6 +2219,16 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1980,6 +2276,16 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2027,6 +2333,16 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2074,6 +2390,16 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2121,6 +2447,16 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2168,6 +2504,16 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2215,6 +2561,16 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2266,6 +2622,16 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2325,6 +2691,16 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2384,6 +2760,16 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2443,6 +2829,16 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2502,6 +2898,16 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2561,6 +2967,16 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2620,6 +3036,16 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2679,6 +3105,16 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2703,7 +3139,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kasteel, 7741 GC</t>
+          <t>Kasteel, 7741 GR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2738,6 +3174,16 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2797,6 +3243,16 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2856,6 +3312,16 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2915,6 +3381,16 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2974,6 +3450,16 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>info@flevoland.nl</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Flevoland | flevoland.nl | Noot: geen apart energiehubs-programma; via RES Flevoland</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3033,6 +3519,16 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3092,6 +3588,16 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3151,6 +3657,16 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3210,6 +3726,16 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3269,6 +3795,16 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3328,6 +3864,16 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3387,6 +3933,16 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3446,6 +4002,16 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3505,6 +4071,16 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3564,6 +4140,16 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3623,6 +4209,16 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3682,6 +4278,16 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3741,6 +4347,16 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3800,6 +4416,16 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3859,6 +4485,16 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3918,6 +4554,16 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3977,6 +4623,16 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4036,6 +4692,16 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4095,6 +4761,16 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4154,6 +4830,16 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4213,6 +4899,16 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4264,6 +4960,16 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4323,6 +5029,16 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4382,6 +5098,16 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4433,6 +5159,16 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4492,6 +5228,16 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4551,6 +5297,16 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4610,6 +5366,16 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4669,6 +5435,16 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4728,6 +5504,16 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4787,6 +5573,16 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4846,6 +5642,16 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4905,6 +5711,16 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4964,6 +5780,16 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5023,6 +5849,16 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5082,6 +5918,16 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5141,6 +5987,16 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5200,6 +6056,16 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5259,6 +6125,16 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5318,6 +6194,16 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5377,6 +6263,16 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5436,6 +6332,16 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5495,6 +6401,16 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5554,6 +6470,16 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5578,7 +6504,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rijksweg A28, 8031 ES</t>
+          <t>Katerdijk, 8031 ES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5613,6 +6539,16 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5672,6 +6608,16 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5731,6 +6677,16 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5790,6 +6746,16 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5849,6 +6815,16 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5908,6 +6884,16 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5932,7 +6918,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Markt 85, 4331 LL</t>
+          <t>Lange Noordstraat 1A, 4331 CB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5967,6 +6953,16 @@
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6026,6 +7022,16 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6085,6 +7091,16 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>rondleidingen@schoonschipamsterdam.org</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Pers: pers@schoonschipamsterdam.org | Johan van Hasseltkade 225-b Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6144,6 +7160,16 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6203,6 +7229,16 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6262,6 +7298,12 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Amsterdam Economic Board / FlexCitizen – flexcitizen.nl</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6321,6 +7363,16 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6380,6 +7432,16 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6439,6 +7501,16 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6498,6 +7570,16 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6557,6 +7639,16 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6616,6 +7708,16 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6675,6 +7777,16 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6734,6 +7846,16 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6793,6 +7915,16 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6852,6 +7984,16 @@
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6911,6 +8053,12 @@
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Richard de Haas, Rijksstraatweg 45, 4103 NH Culemborg (thermobello.nl)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6970,6 +8118,16 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7029,6 +8187,16 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>info@energievanutrecht.nl</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Energie van Utrecht – energievanutrecht.nl</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7088,6 +8256,16 @@
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7147,6 +8325,16 @@
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7206,6 +8394,16 @@
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>info@agem.nl</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Agem / Local4Local – agem.nl/local4local | Doetinchem, Gelderland</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7265,6 +8463,16 @@
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>info@agem.nl</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Agem Energiebedrijf | agem.nl | Doetinchem, Gelderland</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7324,6 +8532,16 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7383,6 +8601,16 @@
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7442,6 +8670,16 @@
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7501,6 +8739,16 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7560,6 +8808,16 @@
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7619,6 +8877,16 @@
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7678,6 +8946,16 @@
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7737,6 +9015,16 @@
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7796,6 +9084,16 @@
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7855,6 +9153,16 @@
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7914,6 +9222,16 @@
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7973,6 +9291,16 @@
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>info@grunnegerpower.nl</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Steven Volkers (directeur), 050-8200492 | Atoomweg 6B, 9743 AK Groningen</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8032,6 +9360,16 @@
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>info@grunnegerpower.nl</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Steven Volkers (directeur), 050-8200492 | Atoomweg 6B, 9743 AK Groningen</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8091,6 +9429,16 @@
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8150,6 +9498,16 @@
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8209,6 +9567,16 @@
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8268,6 +9636,16 @@
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8327,6 +9705,16 @@
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8386,6 +9774,16 @@
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>info@flevoland.nl</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Flevoland | flevoland.nl | Noot: geen apart energiehubs-programma; via RES Flevoland</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8445,6 +9843,16 @@
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8504,6 +9912,16 @@
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8563,6 +9981,16 @@
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8622,6 +10050,16 @@
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8673,6 +10111,16 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>info@tapelectric.app</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>TAP Electric / Power Intel – tapelectric.app | Noord-Brabant</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8724,6 +10172,16 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>info@elaad.nl</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>ElaadNL – elaad.nl | Smart charging testlocatie Zeist</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8779,6 +10237,16 @@
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>info@tealmobility.com</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>TEAL Mobility / TotalEnergies – tealmobility.com | Deventer</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8830,6 +10298,16 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8881,6 +10359,12 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>New Energy Coalition – newenergycoalition.org</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8932,6 +10416,16 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht – Aanpak energiehubs bedrijventerreinen | energietransitieutrecht.nl/energiehub | Kwartiermakers Energiehubs (Stedin + Prov.UT)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8983,6 +10477,16 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>energiehub@weert.nl</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Gemeente Weert – weert.nl | Kampershoek, Limburg</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9038,6 +10542,16 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>info@fastned.nl</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Fastned – fastned.nl | Laadinfrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9093,6 +10607,16 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9152,6 +10676,16 @@
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>info@resato.com</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Resato International – resato.com | Assen</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9207,6 +10741,16 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9262,6 +10806,12 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Provincie Gelderland – gelderland.nl/nieuws | IJzendoorn</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9317,6 +10867,16 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9372,6 +10932,16 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9427,6 +10997,16 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9482,6 +11062,16 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>info@greenpointfuels.nl</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Greenpoint Fuels – greenpointfuels.nl</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9537,6 +11127,16 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>info@watthub.nl</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>WattHub – watthub.nl</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9596,6 +11196,16 @@
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>info@groningen-seaports.com</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Groningen Seaports – groningen-seaports.com | Delfzijl / Eemshaven</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9655,6 +11265,16 @@
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9714,6 +11334,16 @@
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>info@milence.com</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Milence – milence.com | Europese laadhub operator</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9769,6 +11399,16 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>info@greenpointfuels.nl</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Greenpoint Fuels – greenpointfuels.nl</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9824,6 +11464,16 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>info@greenpointfuels.nl</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Greenpoint Fuels – greenpointfuels.nl</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9879,6 +11529,16 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>info@greenpointfuels.nl</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Greenpoint Fuels – greenpointfuels.nl</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9934,6 +11594,12 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Watts in Store / mobiliteit.nl | Roosendaal, Noord-Brabant</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9993,6 +11659,16 @@
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>info@connexxion.nl</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Connexxion – connexxion.nl</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10052,6 +11728,16 @@
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>info@gvb.nl</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>GVB Amsterdam – gvb.nl</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10107,6 +11793,16 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10162,6 +11858,16 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>info@portofamsterdam.com</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Port of Amsterdam – portofamsterdam.com</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10217,6 +11923,16 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>info@aviaweghorst.nl</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>AVIA Weghorst / Brink XL – aviaweghorst.nl | Enter, Overijssel</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10272,6 +11988,16 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>info@fietenenergie.nl</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Fieten Olie / Energie – fietenenergie.nl</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10327,6 +12053,16 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>info@fietenenergie.nl</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Fieten Olie / Energie – fietenenergie.nl</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10382,6 +12118,16 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10441,6 +12187,16 @@
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>wouter@heress.nl</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Wouter Heres (regisseur Broeklanden &amp; Hessenpoort), 06-53737556</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10496,6 +12252,16 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10551,6 +12317,16 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10606,6 +12382,16 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10661,6 +12447,16 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>info@greenpointfuels.nl</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Greenpoint Fuels – greenpointfuels.nl</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10716,6 +12512,16 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>info@tealmobility.com</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>TEAL Mobility – tealmobility.com</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10771,6 +12577,16 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>info@greenpointfuels.nl</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Greenpoint Fuels – greenpointfuels.nl</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10826,6 +12642,16 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10885,6 +12711,12 @@
         </is>
       </c>
       <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Topsector Energie – topsectorenergie.nl/projecten-old/energy-hub-alpherium</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10940,6 +12772,16 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>info@fountainfuel.com</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Fountain Fuel – fountainfuel.com</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10995,6 +12837,16 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>info@htm.nl</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>HTM Den Haag – htm.nl</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11050,6 +12902,16 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>info@portofrotterdam.com</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Port of Rotterdam / LLHDL – portofrotterdam.com</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11109,6 +12971,16 @@
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>info@portofrotterdam.com</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Port of Rotterdam – portofrotterdam.com</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11164,6 +13036,16 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>info@watthub.nl</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>WattHub – watthub.nl</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11219,6 +13101,12 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Gasunie – gasunie.nl/projects/gzi-next | Emmen</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11270,6 +13158,16 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11321,6 +13219,16 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11368,6 +13276,16 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11419,6 +13337,16 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11470,6 +13398,16 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11521,6 +13459,16 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11572,6 +13520,16 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11623,6 +13581,16 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | CoP 'Net op Groen' | provincie.drenthe.nl/onderwerpen/natuur-milieu/diversen/netcongestie/energiehubs-drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11674,6 +13642,16 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>info@energiehubeeserwold.nl</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>energiehubeeserwold.nl | Steenwijkerland, Overijssel</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11725,6 +13703,16 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>info@groningenstroomtdoor.nl</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>groningenstroomtdoor.nl | Groningen</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11776,6 +13764,16 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>f.deboer@energiehub050.nl</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Freddy de Boer (programmadirecteur), 06-51507286</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11823,6 +13821,16 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>info@groningen-seaports.com</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Groningen Seaports – groningen-seaports.com</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11874,6 +13882,16 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11925,6 +13943,16 @@
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>info@north2.eu</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>NortH2 – north2.eu | Groningen / Eemshaven</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11972,6 +14000,16 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>info@provinciegroningen.nl</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Groningen – afd. Energietransitie | 050-3164911 | provinciegroningen.nl | Noot: geen apart energiehubs-loket, vragen via gemeente</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12023,6 +14061,16 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12074,6 +14122,16 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12125,6 +14183,16 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12176,6 +14244,16 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12227,6 +14305,16 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>info@energiecampusleeuwarden.nl</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>energiecampusleeuwarden.nl</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12278,6 +14366,16 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>info@dezwette.nl</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>dezwette.nl | Bedrijvenpark Leeuwarden</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12329,6 +14427,16 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12380,6 +14488,16 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | Friese Energietafel: frieseenergietafel.nl | FREON: freonfryslan.frl</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12431,6 +14549,16 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>wouter@heress.nl</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Wouter Heres (regisseur Broeklanden &amp; Hessenpoort), 06-53737556</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12482,6 +14610,16 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>info@hydronex.nl</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Hydronex – hydronex.nl | Twente</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12533,6 +14671,16 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>beekmanbildung@gmail.com</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Rutger Beekman (regisseur XL Businesspark &amp; A1 Bedrijvenpark), 06-20993838</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12584,6 +14732,16 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>wouter@heress.nl</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Wouter Heres (regisseur Broeklanden &amp; Hessenpoort), 06-53737556</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12608,7 +14766,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Rijksweg A28, 8031 ES</t>
+          <t>Katerdijk, 8031 ES</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12635,6 +14793,16 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Marc Leeuw (projectmanager Energy, Oost NL), 06-48697608 | Robert-Niels van Droffelaar, 06-12600593</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12686,6 +14854,16 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>beekmanbildung@gmail.com</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Rutger Beekman (regisseur XL Businesspark &amp; A1 Bedrijvenpark), 06-20993838</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12737,6 +14915,16 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Dijk en Waard | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12788,6 +14976,16 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Amsterdam | Hubregisseur: Ronald | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12839,6 +15037,16 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Purmerend | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12890,6 +15098,16 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Alkmaar | Hubregisseur: NEC (Sjors van Kuipers) | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12941,6 +15159,16 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Alkmaar | Hubregisseur: NEC (Sjors van Kuipers) | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12992,6 +15220,16 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Beverwijk | Hubregisseur: Ronald | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13043,6 +15281,16 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Velsen | Hubregisseur: Lara Broeder | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13094,6 +15342,16 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Opmeer | Hubregisseur: NEC | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13145,6 +15403,16 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>info@ecah.amsterdam</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>ECAH Amsterdam – ecah.amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13196,6 +15464,16 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13247,6 +15525,16 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13298,6 +15586,16 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Gooische Meren | Hubregisseur: Lea/Anish | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13349,6 +15647,16 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Velsen | Hubregisseur: Ronald | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13400,6 +15708,16 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Medemblik | Hubregisseur: NEC | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13451,6 +15769,16 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Zaanstad | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13502,6 +15830,16 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Hoorn | Hubregisseur: Lea/Anish (Charlotte Bakker) | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13526,7 +15864,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Luchthavenweg, 1786 PP</t>
+          <t>Oostoeverweg, 1786 PT</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -13553,6 +15891,16 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Den Helder | Hubregisseur: NEC (Arnold Boon) | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13604,6 +15952,16 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Hilversum | Hubregisseur: Lea/Anish | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13655,6 +16013,16 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Haarlemmermeer | Hubregisseur: Ronald | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13706,6 +16074,16 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Haarlemmermeer | Fase 2 (onzeker of hub doorgaat)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13757,6 +16135,16 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Zaanstad | Hubregisseur: Tom Grootjen | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13808,6 +16196,16 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Den Helder | Hubregisseur: NEC (Arnold Boon) | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13859,6 +16257,16 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Haarlem | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13910,6 +16318,16 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13961,6 +16379,16 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager Energiehubs NH) | EnergieRegio NH: info@energieregionh.nl | energieregionh.nl/taskforce-e-infra/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14012,6 +16440,16 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Hoorn | Hubregisseur: NEC (Charlotte Bakker) | Fase 2</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14063,6 +16501,16 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>info@energieregionh.nl</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>EnergieRegio NH | Gemeente Dijk en Waard | Hubregisseur: NEC | Fase 1</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14122,6 +16570,16 @@
         </is>
       </c>
       <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>seh@bradipi.com</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Joris Benninga (regisseur De Mars / Zutphen)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14181,6 +16639,16 @@
         </is>
       </c>
       <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>wicha@innoconnect.nl</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Wicha Benus (regisseur Harselaar), 06-53873997</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14240,6 +16708,16 @@
         </is>
       </c>
       <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Marieke Butterhoff (procesregisseur TPN-West) | Marc Leeuw (Oost NL), 06-48697608</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14299,6 +16777,16 @@
         </is>
       </c>
       <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Ruud van Kolfschooten (regisseur InnoFase &amp; Brick Valley) | Jeroen Smits (accountmanager innofase.com) | Marc Leeuw (Oost NL), 06-48697608</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14350,6 +16838,16 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>energie@gelderland.nl</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Gelderland – afd. Energie | Gelders Energieakkoord: geldersenergieakkoord.nl | GWB: gelderswarmtebedrijf.nl | Oost NL SEH: marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14401,6 +16899,16 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Marc Leeuw (projectmanager Energy, Oost NL), 06-48697608</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14452,6 +16960,16 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Ruud van Kolfschooten (regisseur InnoFase &amp; Brick Valley) | Marc Leeuw (Oost NL), 06-48697608</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14503,6 +17021,12 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Ecofactorij Apeldoorn – ecofactorij.nl | Saxion TSE Learning Community</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14554,6 +17078,16 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>thomas@transitiemakers.nl</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Thomas Pesiwarissa (regisseur Lorentz / Harderwijk)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14605,6 +17139,16 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14656,6 +17200,16 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>info@energiekeregio.nl</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>EnergieKe Regio – energiekeregio.nl | Zwijndrecht</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14707,6 +17261,16 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14758,6 +17322,16 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zuid-Holland – Uitvoeringsagenda Stimuleringsprogramma Energiehubs | Innovation Quarter | CoP Energiehubs ZH | zuid-holland.nl/onderwerpen/energie/energie-infrastructuur</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14809,6 +17383,16 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>info@greenparcbleiswijk.nl</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>GreenParc Bleiswijk – greenparcbleiswijk.nl | Bleiswijk</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14860,6 +17444,16 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14911,6 +17505,16 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14962,6 +17566,12 @@
       </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Energiehub De Brand – 's-Hertogenbosch, Noord-Brabant</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15009,6 +17619,16 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15060,6 +17680,16 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>info@mnext.nl</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Mnext / Eersel BT – mnext.nl | Noord-Brabant</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15111,6 +17741,16 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15158,6 +17798,12 @@
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Land van Cuijk – landvancuijk.nl</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15205,6 +17851,12 @@
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Gemeente Bernheze / Oss / 's-Hertogenbosch – heesch-west.nl</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15252,6 +17904,12 @@
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Gemeente Bernheze / Oss / 's-Hertogenbosch – heesch-west.nl</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15299,6 +17957,12 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Gemeente Bernheze / Oss / 's-Hertogenbosch – heesch-west.nl</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15350,6 +18014,12 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>hetkop.nl | Kempenregio, Noord-Brabant</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15401,6 +18071,16 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15448,6 +18128,16 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15495,6 +18185,16 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15542,6 +18242,16 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15593,6 +18303,16 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>info@meierijstad.nl</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>EW Installatietechniek / Meierijstad – ew-installatietechniek.nl</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15644,6 +18364,16 @@
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>info@dekievitbv.nl</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>De Kievit BV – dekievitbv.nl/energiehub | Grashoek, Limburg</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15695,6 +18425,16 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>info@energiekeregio.nl</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>EnergieKe Regio – energiekeregio.nl | Schiedam</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15750,6 +18490,12 @@
       </c>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht / Stedin – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15805,6 +18551,12 @@
       </c>
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15860,6 +18612,12 @@
       </c>
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15915,6 +18673,12 @@
       </c>
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Bas de Haas (aanjager PVB/Prov.UT); Sander Veltmaat (hubregisseur); Rob Tuinenburg (gem. Soest)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15970,6 +18734,12 @@
       </c>
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16025,6 +18795,12 @@
       </c>
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16080,6 +18856,12 @@
       </c>
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16135,6 +18917,12 @@
       </c>
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16190,6 +18978,12 @@
       </c>
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16245,6 +19039,12 @@
       </c>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16300,6 +19100,12 @@
       </c>
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16355,6 +19161,12 @@
       </c>
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16410,6 +19222,12 @@
       </c>
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16465,6 +19283,12 @@
       </c>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16520,6 +19344,12 @@
       </c>
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16575,6 +19405,12 @@
       </c>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16630,6 +19466,12 @@
       </c>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Provincie Utrecht – energietransitieutrecht.nl/energiehub</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16685,6 +19527,16 @@
       </c>
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>energie@bladel.nl</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Gemeente Bladel – bladel.nl/energiehub | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16740,6 +19592,12 @@
       </c>
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Gemeente Breda – breda.nl | Steenakker</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16795,6 +19653,12 @@
       </c>
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Gemeente Breda – breda.nl</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16850,6 +19714,16 @@
       </c>
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16905,6 +19779,12 @@
       </c>
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Gemeente Breda – breda.nl | Steenakker</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16960,6 +19840,16 @@
       </c>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>info@brainporteindhoven.com</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Brainport Eindhoven – brainporteindhoven.com</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -17015,6 +19905,16 @@
       </c>
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -17070,6 +19970,16 @@
       </c>
       <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -17125,6 +20035,16 @@
       </c>
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17180,6 +20100,12 @@
       </c>
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Gemeente Breda – lokaleregelgeving.overheid.nl</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -17235,6 +20161,12 @@
       </c>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Gemeente Breda – lokaleregelgeving.overheid.nl</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17290,6 +20222,16 @@
       </c>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -17345,6 +20287,16 @@
       </c>
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -17400,6 +20352,16 @@
       </c>
       <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -17455,6 +20417,16 @@
       </c>
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17510,6 +20482,16 @@
       </c>
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -17565,6 +20547,16 @@
       </c>
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -17620,6 +20612,16 @@
       </c>
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -17675,6 +20677,16 @@
       </c>
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -17730,6 +20742,16 @@
       </c>
       <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17785,6 +20807,16 @@
       </c>
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17840,6 +20872,12 @@
       </c>
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Roosendaal – lokaleregelgeving.overheid.nl</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -17895,6 +20933,16 @@
       </c>
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17950,6 +20998,16 @@
       </c>
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -18005,6 +21063,16 @@
       </c>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -18060,6 +21128,16 @@
       </c>
       <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -18115,6 +21193,16 @@
       </c>
       <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18170,6 +21258,16 @@
       </c>
       <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>energiehub@maastricht.nl</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Gemeente Maastricht – gemeentemaastricht.nl | Beatrixhaven</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -18225,6 +21323,16 @@
       </c>
       <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>info@weert.nl</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Gemeente Weert – weert.nl | Kampershoek</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18280,6 +21388,16 @@
       </c>
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>info@volantis.nl</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Volantis / Tradeport Venlo – volantis.nl</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18335,6 +21453,16 @@
       </c>
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>info@shiftlimburg.nl</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>Shift Limburg – shiftlimburg.nl | Sittard-Geleen</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18390,6 +21518,16 @@
       </c>
       <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>info@shiftlimburg.nl</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Shift Limburg – shiftlimburg.nl | Heerlen</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -18445,6 +21583,16 @@
       </c>
       <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>info@shiftlimburg.nl</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Shift Limburg – shiftlimburg.nl | Kerkrade</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18500,6 +21648,16 @@
       </c>
       <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>info@shiftlimburg.nl</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Shift Limburg – shiftlimburg.nl | Nuth</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -18555,6 +21713,16 @@
       </c>
       <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg energiehubs | LUPEH: limburg.nl | LWV / OML / LIOF samenwerking | shiftlimburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -18610,6 +21778,16 @@
       </c>
       <c r="L333" t="inlineStr"/>
       <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>info@limburg.nl</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Provincie Limburg – limburg.nl</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -18665,6 +21843,16 @@
       </c>
       <c r="L334" t="inlineStr"/>
       <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>info@logistiekbereikbaar.nl</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Logistiek Bereikbaar – logistiekbereikbaar.nl | Limburg</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18720,6 +21908,16 @@
       </c>
       <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>info@mijnwater.com</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Mijnwater BV – mijnwater.com | Heerlen / Parkstad</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -18775,6 +21973,16 @@
       </c>
       <c r="L336" t="inlineStr"/>
       <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>info@chemelot.nl</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Chemelot – chemelot.nl | Sittard-Geleen / Limburg</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -18826,6 +22034,16 @@
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>info@damen.com</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Damen Shipyards – damen.com | Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18873,6 +22091,12 @@
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
       <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>Circul8 / HyDeer – industrielinqs.nl | Lelystad, Flevoland</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18897,7 +22121,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Rijksweg A28, 8031 ES</t>
+          <t>Katerdijk, 8031 ES</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -18920,6 +22144,16 @@
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
       <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>info@solinoor.com</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Solinoor / Terrazande – solinoor.com | Zwolle</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18967,6 +22201,16 @@
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel (NEO) | Energiehubs contact: Jorian Bakker | nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -19010,6 +22254,12 @@
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
       <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Europawire – news.europawire.eu | Zeewolde, Flevoland</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -19065,6 +22315,16 @@
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
       <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>info@groningen-seaports.com</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>NEO / Groningen Seaports – groningen-seaports.com | Delfzijl</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -19120,6 +22380,16 @@
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>info@groningen-seaports.com</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>GIGA Storage / Groningen Seaports | Delfzijl</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -19175,6 +22445,16 @@
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
       <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>info@vreugdenhilzuivel.nl</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Vreugdenhil Zuivel – cluster6.nl | Scharsterbrug</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -19230,6 +22510,12 @@
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>Cluster 6 – cluster6.nl | Emmen, Drenthe</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -19285,6 +22571,16 @@
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>info@hydronex.nl</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>Hydronex – hydronex.nl | Vriezenveen, Overijssel</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -19344,6 +22640,12 @@
         </is>
       </c>
       <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>VNO-NCW Midden / Oost NL – H2Hub Twente, Almelo</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -19403,6 +22705,12 @@
         </is>
       </c>
       <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Nieuweenergieoverijssel.nl | Hessenpoort Zwolle</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -19458,6 +22766,12 @@
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>Cluster 6 Papierindustrie – cluster6.nl | Brummen, Gelderland</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -19513,6 +22827,16 @@
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>marc.leeuw@oostnl.nl</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Ruud van Kolfschooten (regisseur InnoFase &amp; Brick Valley) | Marc Leeuw (Oost NL), 06-48697608</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -19568,6 +22892,16 @@
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
       <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>info@regiofoodvalley.nl</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>Regio Food Valley – regiofoodvalley.nl | Ede/Wageningen</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -19623,6 +22957,16 @@
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>info@newenergycoalition.org</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>New Energy Coalition – newenergycoalition.org | Alkmaar</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -19678,6 +23022,16 @@
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr"/>
       <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>info@firan.nl</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Firan – firan.nl | Zaanstad, Noord-Holland</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -19733,6 +23087,12 @@
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>Provincie Noord-Holland / Cluster 6 – cluster6.nl</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19788,6 +23148,16 @@
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>info@vreugdenhilzuivel.nl</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>Vreugdenhil Zuivel – cluster6.nl | Gorinchem</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -19843,6 +23213,12 @@
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Provincie Zuid-Holland / Cluster 6 – cluster6.nl</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19898,6 +23274,16 @@
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
       <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>info@regiofoodvalley.nl</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Regio Food Valley – regiofoodvalley.nl | Ede/Wageningen</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19953,6 +23339,16 @@
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>info@chemelot.nl</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Chemelot – chemelot.nl | Sittard-Geleen</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -20008,6 +23404,16 @@
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr"/>
       <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>info@zeeland.nl</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Zeeland – afd. Energie &amp; Klimaat | +31 118 631011 | zeeland.nl/energie-en-klimaat | Zeeuws Klimaatfonds: zeeuwsklimaat.nl</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -20071,6 +23477,16 @@
         </is>
       </c>
       <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -20134,6 +23550,16 @@
         </is>
       </c>
       <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -20197,6 +23623,16 @@
         </is>
       </c>
       <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -20260,6 +23696,16 @@
         </is>
       </c>
       <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -20323,6 +23769,16 @@
         </is>
       </c>
       <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (projectmanager energie &amp; ruimtelijke ontwikkeling, Prov. NB) | brabant.nl/onderwerpen/energie/elektriciteit/energiehubs | EWB: energiewerkplaatsbrabant.nl</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -20388,6 +23844,3774 @@
       <c r="M365" t="inlineStr">
         <is>
           <t>Groepscontract (virtueel net)</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>PVB Nederland – pvbnederland.nl | 15 bedrijven, virtueel net Liander | case jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Energiehub Riegmeer</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://www.rendonetwerken.nl/zakelijk/netcapaciteit/toekomstige-vermogensbehoefte-riegmeer/</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Drenthe</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Hoogeveen</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | RENDO</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Waterstof, Groen gas</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | energiehubs@drenthe.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>MCEH Werklandschap Assen-Zuid</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Drenthe</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Assen</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>energiehubs@drenthe.nl</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Projectorganisatie Energiehubs Drenthe | energiehubs@drenthe.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SEH BEtterwird</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://raboenco.rabobank.nl/nl/articles/107255/</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Friesland</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Dokkum</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>energie@fryslan.frl</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Fryslân – team Klimaat &amp; Energie | energie@fryslan.frl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Energie Handels Platform-Pannenweg B.V.</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Limburg</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Nederweert</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Fase 4: Exploiteren</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>info@liof.nl</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: LIOF / Provincie Limburg | info@liof.nl | LUPEH-programma | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Theodorushaven/ Noordland/DePoort</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Bergen op Zoom</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Energiehub Oude Molen</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Halsteren</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Energiehub LMM</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Bergen op Zoom</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Ehub Dintelmond</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Heijningen</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Koude</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Energyhub Vlasweg - Port of Moerdijk</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Moerdijk</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Waterstof, Groen gas</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Energiehub Everdenberg-Oost</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Oosterhout</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Energiehub De Hurk</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://www.dehurkwerkt.nl/</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Waterstof, Warmte</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Energiehub Tilburg Zuid</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: On hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Energiehub Kraaiven - Vossenberg</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr"/>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Energiehub Loven</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Grote Oogst Moleneind</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Oss</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Energyhub bedrijventerrein Uden</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Uden</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Groen gas</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Energie Hub Duin Schijndel</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Schijndel</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Haalbaarheidsstudie Energiehub Elzenburg-de Geer</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Oss</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Haalbaarheidsstudie energie hub Asten</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Asten</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Lokaal Collectief Energiesysteem / LCE</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://lceveghel.nl/</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Veghel</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Koude, Waterstof</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>e-Hub Majoppeveld</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Roosendaal</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Energie Verkenning Borchwerf I</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Roosendaal</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | brabant.nl/energiehubs | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>De President (SADC)</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Hoofddorp</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Fase 3: Realiseren</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Sloterdijk Westpoort</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein Business Docks - Cluster 4</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Beverwijk</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>EHUB-Eco congestie loket Weesp</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Weesp</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Fase 3: Realiseren</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>EHUB IVW-Weesp Duurzaam Initiatief</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Weesp</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Fase 3: Realiseren</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Smart Grid Walstroom</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Den Helder</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>IJmuiden haven</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>IJmuiden</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Kennispark</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Zeearend</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Josink Es</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Marssteden</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Gestopt</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Turfkade</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Goor De Whee en Spechthorst</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Goor</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Gestopt</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Stepelo</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Haaksbergen</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Brammelo en 't Varck</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Haaksbergen</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Katingerveld &amp; Rollepaal zuid</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Dedemsvaart</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Twentekanaal (HTSP)</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Hengelo</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Haatlandhaven &amp; Esstraat</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>De pol</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Losser</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Zoeker Esch</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Losser</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Eekte-Hazewinkel</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Oldenzaal</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Gestopt</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Rotbrink</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Ommen</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>De Zegge</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Raalte</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>De Mors</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Rijssen</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Vletgaarsmaten/ de Haar (Holten)</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Holten</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>De Esch</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Staphorst</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Groot Verlaat</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Steenwijk</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Tubbergen</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Tubbergen</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>De Sluis, Linderflier</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Vroomshoop</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>SEH ATT</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Vriezenveen</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Zevenhont</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Genemuiden</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Marslanden</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Het Blauwe Hart (OVB)</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Meppelerdiep/ Zomerdijk/ Buitenkwartier</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Zwartewaterland</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Hasselt</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://nieuweenergieoverijssel.nl/onderwerpen/energiehubs</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Hasselt</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>CEURZ</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://energiecooperatiehessenpoort.nl/</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Overijssel</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Fase 4: Exploiteren</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>secretariaatNEO@overijssel.nl</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Nieuwe Energie Overijssel | secretariaatNEO@overijssel.nl | Jorian Bakker (SEH) | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Het Ambacht</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://www.energietransitieutrecht.nl/onderwerpen/innovatie-energietransitie/aanpak-energiehubs-op-bedrijventerreinen</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Veenendaal</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Stedin</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Koude</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht | energiehub@provincie-utrecht.nl | Stedin samenwerking | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Factorij De Vendel</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://www.energietransitieutrecht.nl/onderwerpen/innovatie-energietransitie/aanpak-energiehubs-op-bedrijventerreinen</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Veenendaal</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Stedin</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht | energiehub@provincie-utrecht.nl | Stedin samenwerking | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Nijvercampus</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://www.energietransitieutrecht.nl/onderwerpen/innovatie-energietransitie/aanpak-energiehubs-op-bedrijventerreinen</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Veenendaal</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Stedin</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Koude</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht | energiehub@provincie-utrecht.nl | Stedin samenwerking | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>EHUB Mijdrecht-Duurzaamheidspartners</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Mijdrecht</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Stedin</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht | energiehub@provincie-utrecht.nl | Stedin samenwerking | Status: On hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Energiehub Fascinatio</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Zuid-Holland</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Capelle aan den IJssel</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Stedin</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>energie-infrastructuur@pzh.nl</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie ZH – Uitvoeringsagenda Energiehubs | energie-infrastructuur@pzh.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>EHUB de Corridor</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Breukelen</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Stedin</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>energiehub@provincie-utrecht.nl</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Provincie Utrecht | energiehub@provincie-utrecht.nl | Stedin samenwerking | Status: On hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Boekelermeer Energy Valley</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://www.alkmaar.nl/projecten-en-nieuwbouw/energiehub/</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Alkmaar</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Fase 3: Realiseren</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Liander</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Elektriciteit, Warmte, Waterstof, Groen gas</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Ron.de.graaf@noord-holland.nl</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Ron de Graaf (programmamanager) | Ron.de.graaf@noord-holland.nl | Status: Actief</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Energiehub Habraken</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://energiehubs.nl/initiatieven</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Noord-Brabant</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Veldhoven</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Fase 1: Verkennen</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Energiehubs.nl initiatievenradar | Enexis</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Elektriciteit</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>energiehubs@brabant.nl</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>🏛️ Prov. contact: Marc van de Ven (Prov. NB) | energiehubs@brabant.nl | Status: Actief</t>
         </is>
       </c>
     </row>

--- a/Energiehubs_Uniform_Fases_RES_REGIO.xlsx
+++ b/Energiehubs_Uniform_Fases_RES_REGIO.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generaal Spoorlaan, 2283 GA</t>
+          <t>Burgemeester Elsenlaan, 2282 NE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kasteel, 7741 GR</t>
+          <t>Kasteel, 7741 GC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Katerdijk, 8031 ES</t>
+          <t>Rijksweg A28, 8031 ES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lange Noordstraat 1A, 4331 CB</t>
+          <t>Markt 85, 4331 LL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Katerdijk, 8031 ES</t>
+          <t>Rijksweg A28, 8031 ES</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Oostoeverweg, 1786 PT</t>
+          <t>Luchthavenweg, 1786 PP</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Veemarktkade, 5222 AE</t>
+          <t>Veemarktkade, 5222 AG</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Katerdijk, 8031 ES</t>
+          <t>Rijksweg A28, 8031 ES</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -23657,7 +23657,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Veemarktkade, 5222 AE</t>
+          <t>Veemarktkade, 5222 AG</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -23874,13 +23874,21 @@
           <t>Hoogeveen</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Riegmeer, Hoogeveen</t>
+        </is>
+      </c>
       <c r="F366" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>52.6968, 6.5235</t>
+        </is>
+      </c>
       <c r="H366" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -23891,7 +23899,11 @@
           <t>Energiehubs.nl initiatievenradar | RENDO</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr"/>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Drenthe</t>
+        </is>
+      </c>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
@@ -23931,13 +23943,21 @@
           <t>Assen</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Werklandschap Assen-Zuid, Assen</t>
+        </is>
+      </c>
       <c r="F367" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>52.9830, 6.5630</t>
+        </is>
+      </c>
       <c r="H367" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -23948,7 +23968,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J367" t="inlineStr"/>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Drenthe</t>
+        </is>
+      </c>
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
@@ -23988,13 +24012,21 @@
           <t>Dokkum</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Betterwird, Dokkum</t>
+        </is>
+      </c>
       <c r="F368" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>53.3253, 5.9987</t>
+        </is>
+      </c>
       <c r="H368" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24005,7 +24037,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr"/>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Friesland</t>
+        </is>
+      </c>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
@@ -24045,13 +24081,21 @@
           <t>Nederweert</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Pannenweg, Nederweert</t>
+        </is>
+      </c>
       <c r="F369" t="inlineStr">
         <is>
           <t>Fase 4: Exploiteren</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>51.2812, 5.7502</t>
+        </is>
+      </c>
       <c r="H369" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24062,7 +24106,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Noord- en Midden Limburg</t>
+        </is>
+      </c>
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
@@ -24102,13 +24150,21 @@
           <t>Bergen op Zoom</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Theodorushaven, Bergen op Zoom</t>
+        </is>
+      </c>
       <c r="F370" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>51.5099, 4.2598</t>
+        </is>
+      </c>
       <c r="H370" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24119,7 +24175,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr"/>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
@@ -24159,13 +24219,21 @@
           <t>Halsteren</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Oude Molen, Halsteren</t>
+        </is>
+      </c>
       <c r="F371" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>51.5175, 4.2920</t>
+        </is>
+      </c>
       <c r="H371" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24176,7 +24244,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr"/>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
@@ -24216,13 +24288,21 @@
           <t>Bergen op Zoom</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Ladonkseweg, Bergen op Zoom</t>
+        </is>
+      </c>
       <c r="F372" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>51.5031, 4.3012</t>
+        </is>
+      </c>
       <c r="H372" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24233,7 +24313,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr"/>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
@@ -24273,13 +24357,21 @@
           <t>Heijningen</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Dintelmond, Heijningen</t>
+        </is>
+      </c>
       <c r="F373" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>51.6335, 4.5098</t>
+        </is>
+      </c>
       <c r="H373" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24290,7 +24382,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr"/>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr">
         <is>
@@ -24330,13 +24426,21 @@
           <t>Moerdijk</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Vlasweg, Moerdijk</t>
+        </is>
+      </c>
       <c r="F374" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>51.6850, 4.5740</t>
+        </is>
+      </c>
       <c r="H374" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24387,13 +24491,21 @@
           <t>Oosterhout</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Everdenberg-Oost, Oosterhout</t>
+        </is>
+      </c>
       <c r="F375" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>51.6340, 4.8620</t>
+        </is>
+      </c>
       <c r="H375" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24404,7 +24516,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr"/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
@@ -24444,13 +24560,21 @@
           <t>Eindhoven</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>De Hurk, Eindhoven</t>
+        </is>
+      </c>
       <c r="F376" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>51.4197, 5.4580</t>
+        </is>
+      </c>
       <c r="H376" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24461,7 +24585,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr"/>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Metropoolregio Eindhoven</t>
+        </is>
+      </c>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
@@ -24501,13 +24629,21 @@
           <t>Tilburg</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Tilburg-Zuid, Tilburg</t>
+        </is>
+      </c>
       <c r="F377" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>51.5380, 5.0800</t>
+        </is>
+      </c>
       <c r="H377" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24518,7 +24654,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr"/>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Hart van Brabant</t>
+        </is>
+      </c>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
@@ -24558,13 +24698,21 @@
           <t>Tilburg</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Kraaiven, Tilburg</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>51.5550, 5.0480</t>
+        </is>
+      </c>
       <c r="H378" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24575,7 +24723,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr"/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Hart van Brabant</t>
+        </is>
+      </c>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
@@ -24615,13 +24767,21 @@
           <t>Tilburg</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Loven, Tilburg</t>
+        </is>
+      </c>
       <c r="F379" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>51.5760, 5.0690</t>
+        </is>
+      </c>
       <c r="H379" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24632,7 +24792,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Hart van Brabant</t>
+        </is>
+      </c>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
@@ -24672,13 +24836,21 @@
           <t>Oss</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Moleneind, Oss</t>
+        </is>
+      </c>
       <c r="F380" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>51.7630, 5.5230</t>
+        </is>
+      </c>
       <c r="H380" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24689,7 +24861,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Noord-oost Brabant</t>
+        </is>
+      </c>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
@@ -24729,13 +24905,21 @@
           <t>Uden</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein Uden</t>
+        </is>
+      </c>
       <c r="F381" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>51.6590, 5.6140</t>
+        </is>
+      </c>
       <c r="H381" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24746,7 +24930,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Noord-oost Brabant</t>
+        </is>
+      </c>
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
@@ -24786,13 +24974,21 @@
           <t>Schijndel</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Duin, Schijndel</t>
+        </is>
+      </c>
       <c r="F382" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>51.6270, 5.4170</t>
+        </is>
+      </c>
       <c r="H382" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24803,7 +24999,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr"/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Noord-oost Brabant</t>
+        </is>
+      </c>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
@@ -24843,13 +25043,21 @@
           <t>Oss</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Elzenburg-De Geer, Oss</t>
+        </is>
+      </c>
       <c r="F383" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>51.7450, 5.5350</t>
+        </is>
+      </c>
       <c r="H383" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24860,7 +25068,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr"/>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Noord-oost Brabant</t>
+        </is>
+      </c>
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr">
         <is>
@@ -24900,13 +25112,21 @@
           <t>Asten</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Asten, Asten</t>
+        </is>
+      </c>
       <c r="F384" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>51.3994, 5.7480</t>
+        </is>
+      </c>
       <c r="H384" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24917,7 +25137,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Metropoolregio Eindhoven</t>
+        </is>
+      </c>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
@@ -24957,13 +25181,21 @@
           <t>Veghel</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Amert, Veghel</t>
+        </is>
+      </c>
       <c r="F385" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>51.6420, 5.5390</t>
+        </is>
+      </c>
       <c r="H385" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -24974,7 +25206,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Noord-oost Brabant</t>
+        </is>
+      </c>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr">
         <is>
@@ -25014,13 +25250,21 @@
           <t>Roosendaal</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Majoppeveld, Roosendaal</t>
+        </is>
+      </c>
       <c r="F386" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>51.5240, 4.4800</t>
+        </is>
+      </c>
       <c r="H386" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25031,7 +25275,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
@@ -25071,13 +25319,21 @@
           <t>Roosendaal</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Borchwerf, Roosendaal</t>
+        </is>
+      </c>
       <c r="F387" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>51.5470, 4.4960</t>
+        </is>
+      </c>
       <c r="H387" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25088,7 +25344,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J387" t="inlineStr"/>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>West-Brabant</t>
+        </is>
+      </c>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
@@ -25128,13 +25388,21 @@
           <t>Hoofddorp</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>De President, Hoofddorp</t>
+        </is>
+      </c>
       <c r="F388" t="inlineStr">
         <is>
           <t>Fase 3: Realiseren</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>52.2640, 4.7320</t>
+        </is>
+      </c>
       <c r="H388" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25145,7 +25413,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr"/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Noord-Holland Zuid</t>
+        </is>
+      </c>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
@@ -25185,13 +25457,21 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Westpoort, Amsterdam</t>
+        </is>
+      </c>
       <c r="F389" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>52.3984, 4.8160</t>
+        </is>
+      </c>
       <c r="H389" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25202,7 +25482,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Noord-Holland Zuid</t>
+        </is>
+      </c>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr">
         <is>
@@ -25242,13 +25526,21 @@
           <t>Beverwijk</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Business Docks, Beverwijk</t>
+        </is>
+      </c>
       <c r="F390" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>52.4950, 4.6480</t>
+        </is>
+      </c>
       <c r="H390" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25259,7 +25551,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr"/>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Noord-Holland Zuid</t>
+        </is>
+      </c>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
@@ -25299,13 +25595,21 @@
           <t>Weesp</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Nijverheidsgebied Weesp</t>
+        </is>
+      </c>
       <c r="F391" t="inlineStr">
         <is>
           <t>Fase 3: Realiseren</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>52.3080, 5.0490</t>
+        </is>
+      </c>
       <c r="H391" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25316,7 +25620,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J391" t="inlineStr"/>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Noord-Holland Zuid</t>
+        </is>
+      </c>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
@@ -25356,13 +25664,21 @@
           <t>Weesp</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Industrieweg, Weesp</t>
+        </is>
+      </c>
       <c r="F392" t="inlineStr">
         <is>
           <t>Fase 3: Realiseren</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>52.3095, 5.0520</t>
+        </is>
+      </c>
       <c r="H392" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25373,7 +25689,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr"/>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Noord-Holland Zuid</t>
+        </is>
+      </c>
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
@@ -25413,13 +25733,21 @@
           <t>Den Helder</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Haven Den Helder</t>
+        </is>
+      </c>
       <c r="F393" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>52.9540, 4.7800</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25470,13 +25798,21 @@
           <t>IJmuiden</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Havenkwartier, IJmuiden</t>
+        </is>
+      </c>
       <c r="F394" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>52.4650, 4.5980</t>
+        </is>
+      </c>
       <c r="H394" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25487,7 +25823,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr"/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Noord-Holland Zuid</t>
+        </is>
+      </c>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
@@ -25527,13 +25867,21 @@
           <t>Enschede</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Kennispark Twente, Enschede</t>
+        </is>
+      </c>
       <c r="F395" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>52.2370, 6.8530</t>
+        </is>
+      </c>
       <c r="H395" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25544,7 +25892,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr"/>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
@@ -25584,13 +25936,21 @@
           <t>Almelo</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Zeearend, Almelo</t>
+        </is>
+      </c>
       <c r="F396" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>52.3650, 6.7050</t>
+        </is>
+      </c>
       <c r="H396" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25601,7 +25961,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr"/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
@@ -25641,13 +26005,21 @@
           <t>Enschede</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Josink Es, Enschede</t>
+        </is>
+      </c>
       <c r="F397" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>52.2140, 6.8750</t>
+        </is>
+      </c>
       <c r="H397" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25658,7 +26030,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
@@ -25698,13 +26074,21 @@
           <t>Enschede</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Marssteden, Enschede</t>
+        </is>
+      </c>
       <c r="F398" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>52.2090, 6.8950</t>
+        </is>
+      </c>
       <c r="H398" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25715,7 +26099,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
@@ -25755,13 +26143,21 @@
           <t>Almelo</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Turfkade, Almelo</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>52.3530, 6.6690</t>
+        </is>
+      </c>
       <c r="H399" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25772,7 +26168,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J399" t="inlineStr"/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
@@ -25812,13 +26212,21 @@
           <t>Goor</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>De Whee, Goor</t>
+        </is>
+      </c>
       <c r="F400" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>52.2320, 6.5830</t>
+        </is>
+      </c>
       <c r="H400" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25829,7 +26237,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J400" t="inlineStr"/>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
@@ -25869,13 +26281,21 @@
           <t>Haaksbergen</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Stepelo, Haaksbergen</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>52.1470, 6.7370</t>
+        </is>
+      </c>
       <c r="H401" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25886,7 +26306,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J401" t="inlineStr"/>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
@@ -25926,13 +26350,21 @@
           <t>Haaksbergen</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Brammelo, Haaksbergen</t>
+        </is>
+      </c>
       <c r="F402" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>52.1380, 6.7500</t>
+        </is>
+      </c>
       <c r="H402" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -25943,7 +26375,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr"/>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
@@ -25983,13 +26419,21 @@
           <t>Dedemsvaart</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Katingerveld, Dedemsvaart</t>
+        </is>
+      </c>
       <c r="F403" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>52.5890, 6.5700</t>
+        </is>
+      </c>
       <c r="H403" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26000,7 +26444,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J403" t="inlineStr"/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
@@ -26040,13 +26488,21 @@
           <t>Hengelo</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Twentekanaal HTSP, Hengelo</t>
+        </is>
+      </c>
       <c r="F404" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>52.2600, 6.7930</t>
+        </is>
+      </c>
       <c r="H404" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26057,7 +26513,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
@@ -26097,13 +26557,21 @@
           <t>Kampen</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Haatlandhaven, Kampen</t>
+        </is>
+      </c>
       <c r="F405" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>52.5480, 5.9110</t>
+        </is>
+      </c>
       <c r="H405" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26114,7 +26582,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr">
         <is>
@@ -26154,13 +26626,21 @@
           <t>Losser</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>De Pol, Losser</t>
+        </is>
+      </c>
       <c r="F406" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>52.2590, 7.0010</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26171,7 +26651,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J406" t="inlineStr"/>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr">
         <is>
@@ -26211,13 +26695,21 @@
           <t>Losser</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Zoeker Esch, Losser</t>
+        </is>
+      </c>
       <c r="F407" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>52.2660, 6.9830</t>
+        </is>
+      </c>
       <c r="H407" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26228,7 +26720,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J407" t="inlineStr"/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr">
         <is>
@@ -26268,13 +26764,21 @@
           <t>Oldenzaal</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Eekte, Oldenzaal</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>52.3100, 6.9220</t>
+        </is>
+      </c>
       <c r="H408" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26285,7 +26789,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J408" t="inlineStr"/>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr">
         <is>
@@ -26325,13 +26833,21 @@
           <t>Ommen</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Rotbrink, Ommen</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>52.5140, 6.4200</t>
+        </is>
+      </c>
       <c r="H409" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26342,7 +26858,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
@@ -26382,13 +26902,21 @@
           <t>Raalte</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>De Zegge, Raalte</t>
+        </is>
+      </c>
       <c r="F410" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>52.3840, 6.2890</t>
+        </is>
+      </c>
       <c r="H410" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26399,7 +26927,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr"/>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
@@ -26439,13 +26971,21 @@
           <t>Rijssen</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>De Mors, Rijssen</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>52.3090, 6.5010</t>
+        </is>
+      </c>
       <c r="H411" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26456,7 +26996,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J411" t="inlineStr"/>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
@@ -26496,13 +27040,21 @@
           <t>Holten</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Vletgaarsmaten, Holten</t>
+        </is>
+      </c>
       <c r="F412" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>52.2850, 6.4430</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26513,7 +27065,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr"/>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr">
         <is>
@@ -26553,13 +27109,21 @@
           <t>Staphorst</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>De Esch, Staphorst</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>52.6360, 6.2030</t>
+        </is>
+      </c>
       <c r="H413" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26570,7 +27134,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J413" t="inlineStr"/>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr">
         <is>
@@ -26610,13 +27178,21 @@
           <t>Steenwijk</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Groot Verlaat, Steenwijk</t>
+        </is>
+      </c>
       <c r="F414" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>52.7960, 6.1220</t>
+        </is>
+      </c>
       <c r="H414" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26627,7 +27203,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J414" t="inlineStr"/>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr">
         <is>
@@ -26667,13 +27247,21 @@
           <t>Tubbergen</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein Tubbergen</t>
+        </is>
+      </c>
       <c r="F415" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>52.4070, 6.7920</t>
+        </is>
+      </c>
       <c r="H415" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26684,7 +27272,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J415" t="inlineStr"/>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
@@ -26724,13 +27316,21 @@
           <t>Vroomshoop</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Linderflier, Vroomshoop</t>
+        </is>
+      </c>
       <c r="F416" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>52.4640, 6.5690</t>
+        </is>
+      </c>
       <c r="H416" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26741,7 +27341,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J416" t="inlineStr"/>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
@@ -26781,13 +27385,21 @@
           <t>Vriezenveen</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Vriezenveen, Twenterand</t>
+        </is>
+      </c>
       <c r="F417" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>52.4090, 6.6160</t>
+        </is>
+      </c>
       <c r="H417" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26798,7 +27410,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J417" t="inlineStr"/>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
@@ -26838,13 +27454,21 @@
           <t>Genemuiden</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Zevenhont, Genemuiden</t>
+        </is>
+      </c>
       <c r="F418" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>52.6230, 5.9980</t>
+        </is>
+      </c>
       <c r="H418" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26855,7 +27479,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J418" t="inlineStr"/>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr">
         <is>
@@ -26895,13 +27523,21 @@
           <t>Zwolle</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Marslanden, Zwolle</t>
+        </is>
+      </c>
       <c r="F419" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>52.5130, 6.0990</t>
+        </is>
+      </c>
       <c r="H419" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26912,7 +27548,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J419" t="inlineStr"/>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr">
         <is>
@@ -26952,13 +27592,21 @@
           <t>Zwolle</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Hessenpoort, Zwolle</t>
+        </is>
+      </c>
       <c r="F420" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>52.5350, 6.0630</t>
+        </is>
+      </c>
       <c r="H420" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -26969,7 +27617,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr"/>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr">
         <is>
@@ -27009,13 +27661,21 @@
           <t>Zwartewaterland</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Meppelerdiep, Zwartewaterland</t>
+        </is>
+      </c>
       <c r="F421" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>52.6100, 6.1020</t>
+        </is>
+      </c>
       <c r="H421" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27026,7 +27686,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J421" t="inlineStr"/>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
@@ -27066,13 +27730,21 @@
           <t>Hasselt</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Bedrijventerrein Hasselt</t>
+        </is>
+      </c>
       <c r="F422" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>52.5940, 6.0820</t>
+        </is>
+      </c>
       <c r="H422" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27083,7 +27755,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J422" t="inlineStr"/>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr">
         <is>
@@ -27123,13 +27799,21 @@
           <t>Zwolle</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Hessenpoort, Zwolle</t>
+        </is>
+      </c>
       <c r="F423" t="inlineStr">
         <is>
           <t>Fase 4: Exploiteren</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>52.5350, 6.0630</t>
+        </is>
+      </c>
       <c r="H423" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27140,7 +27824,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J423" t="inlineStr"/>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>West-Overijssel</t>
+        </is>
+      </c>
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr">
         <is>
@@ -27180,13 +27868,21 @@
           <t>Veenendaal</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Het Ambacht, Veenendaal</t>
+        </is>
+      </c>
       <c r="F424" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>52.0390, 5.5640</t>
+        </is>
+      </c>
       <c r="H424" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27197,7 +27893,11 @@
           <t>Energiehubs.nl initiatievenradar | Stedin</t>
         </is>
       </c>
-      <c r="J424" t="inlineStr"/>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>FoodValley</t>
+        </is>
+      </c>
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr">
         <is>
@@ -27237,13 +27937,21 @@
           <t>Veenendaal</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>De Vendel, Veenendaal</t>
+        </is>
+      </c>
       <c r="F425" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>52.0310, 5.5550</t>
+        </is>
+      </c>
       <c r="H425" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27254,7 +27962,11 @@
           <t>Energiehubs.nl initiatievenradar | Stedin</t>
         </is>
       </c>
-      <c r="J425" t="inlineStr"/>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>FoodValley</t>
+        </is>
+      </c>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
@@ -27294,13 +28006,21 @@
           <t>Veenendaal</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Nijvercampus, Veenendaal</t>
+        </is>
+      </c>
       <c r="F426" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>52.0350, 5.5490</t>
+        </is>
+      </c>
       <c r="H426" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27311,7 +28031,11 @@
           <t>Energiehubs.nl initiatievenradar | Stedin</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr"/>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>FoodValley</t>
+        </is>
+      </c>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
@@ -27351,13 +28075,21 @@
           <t>Mijdrecht</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Mijdrecht, De Ronde Venen</t>
+        </is>
+      </c>
       <c r="F427" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>52.2140, 4.8630</t>
+        </is>
+      </c>
       <c r="H427" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27368,7 +28100,11 @@
           <t>Energiehubs.nl initiatievenradar | Stedin</t>
         </is>
       </c>
-      <c r="J427" t="inlineStr"/>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>U10/U16</t>
+        </is>
+      </c>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
@@ -27408,13 +28144,21 @@
           <t>Capelle aan den IJssel</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Fascinatio, Capelle aan den IJssel</t>
+        </is>
+      </c>
       <c r="F428" t="inlineStr">
         <is>
           <t>Fase 2: Plannen &amp; Ontwerpen</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>51.9320, 4.5930</t>
+        </is>
+      </c>
       <c r="H428" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27425,7 +28169,11 @@
           <t>Energiehubs.nl initiatievenradar | Stedin</t>
         </is>
       </c>
-      <c r="J428" t="inlineStr"/>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Rotterdam-Den Haag</t>
+        </is>
+      </c>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
@@ -27465,13 +28213,21 @@
           <t>Breukelen</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Breukelen, Stichtse Vecht</t>
+        </is>
+      </c>
       <c r="F429" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>52.1720, 4.9910</t>
+        </is>
+      </c>
       <c r="H429" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27482,7 +28238,11 @@
           <t>Energiehubs.nl initiatievenradar | Stedin</t>
         </is>
       </c>
-      <c r="J429" t="inlineStr"/>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>U10/U16</t>
+        </is>
+      </c>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr">
         <is>
@@ -27522,13 +28282,21 @@
           <t>Alkmaar</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Boekelermeer, Alkmaar</t>
+        </is>
+      </c>
       <c r="F430" t="inlineStr">
         <is>
           <t>Fase 3: Realiseren</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>52.6320, 4.7720</t>
+        </is>
+      </c>
       <c r="H430" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27539,7 +28307,11 @@
           <t>Energiehubs.nl initiatievenradar | Liander</t>
         </is>
       </c>
-      <c r="J430" t="inlineStr"/>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Noord Holland Noord</t>
+        </is>
+      </c>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
@@ -27579,13 +28351,21 @@
           <t>Veldhoven</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Habraken, Veldhoven</t>
+        </is>
+      </c>
       <c r="F431" t="inlineStr">
         <is>
           <t>Fase 1: Verkennen</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>51.4100, 5.3850</t>
+        </is>
+      </c>
       <c r="H431" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
@@ -27596,7 +28376,11 @@
           <t>Energiehubs.nl initiatievenradar | Enexis</t>
         </is>
       </c>
-      <c r="J431" t="inlineStr"/>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Metropoolregio Eindhoven</t>
+        </is>
+      </c>
       <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr">
         <is>
